--- a/excelfile/myfile.xlsx
+++ b/excelfile/myfile.xlsx
@@ -494,108 +494,168 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>编号</t>
+          <t>地址</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>地址</t>
+          <t>价格（元）</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>价格</t>
+          <t>面积（㎡）</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>租金/月</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>深圳市南山区某小区A栋1室</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>地点A</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>100万</t>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>高层</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1500</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>深圳市南山区某小区B栋2室</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>地点B</t>
+          <t>18000</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>120万</t>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>中层</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1400</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>深圳市南山区某小区C栋3室</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>地点C</t>
+          <t>22000</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>90万</t>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>低层</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1600</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>深圳市南山区某小区D栋4室</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>地点D</t>
+          <t>21000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>110万</t>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>高层</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1550</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>深圳市南山区某小区E栋5室</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>地点E</t>
+          <t>19000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>95万</t>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>中层</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1450</t>
         </is>
       </c>
     </row>
